--- a/Caracterizacion_Haces/data/z14mm-852.xlsx
+++ b/Caracterizacion_Haces/data/z14mm-852.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="137">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,298 +128,313 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-752,5</t>
+    <t>707,9</t>
+  </si>
+  <si>
+    <t>166,9</t>
+  </si>
+  <si>
+    <t>156,7</t>
+  </si>
+  <si>
+    <t>203,3</t>
+  </si>
+  <si>
+    <t>105,2</t>
+  </si>
+  <si>
+    <t>154,3</t>
+  </si>
+  <si>
+    <t>137,2</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>708,4</t>
+  </si>
+  <si>
+    <t>166,0</t>
+  </si>
+  <si>
+    <t>202,9</t>
+  </si>
+  <si>
+    <t>104,7</t>
+  </si>
+  <si>
+    <t>152,9</t>
+  </si>
+  <si>
+    <t>137,1</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>708,2</t>
+  </si>
+  <si>
+    <t>166,2</t>
+  </si>
+  <si>
+    <t>156,4</t>
+  </si>
+  <si>
+    <t>202,3</t>
+  </si>
+  <si>
+    <t>105,6</t>
+  </si>
+  <si>
+    <t>153,7</t>
+  </si>
+  <si>
+    <t>138,0</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>166,1</t>
+  </si>
+  <si>
+    <t>157,8</t>
+  </si>
+  <si>
+    <t>203,2</t>
+  </si>
+  <si>
+    <t>105,8</t>
+  </si>
+  <si>
+    <t>138,3</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>708,7</t>
+  </si>
+  <si>
+    <t>167,0</t>
+  </si>
+  <si>
+    <t>157,5</t>
+  </si>
+  <si>
+    <t>204,1</t>
+  </si>
+  <si>
+    <t>105,1</t>
+  </si>
+  <si>
+    <t>153,1</t>
+  </si>
+  <si>
+    <t>136,9</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>166,4</t>
+  </si>
+  <si>
+    <t>156,6</t>
+  </si>
+  <si>
+    <t>203,1</t>
+  </si>
+  <si>
+    <t>153,9</t>
+  </si>
+  <si>
+    <t>137,7</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>707,4</t>
+  </si>
+  <si>
+    <t>166,8</t>
+  </si>
+  <si>
+    <t>156,5</t>
+  </si>
+  <si>
+    <t>202,7</t>
+  </si>
+  <si>
+    <t>106,0</t>
+  </si>
+  <si>
+    <t>153,8</t>
+  </si>
+  <si>
+    <t>137,5</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>165,7</t>
+  </si>
+  <si>
+    <t>156,0</t>
+  </si>
+  <si>
+    <t>201,4</t>
+  </si>
+  <si>
+    <t>106,2</t>
+  </si>
+  <si>
+    <t>153,4</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>706,6</t>
+  </si>
+  <si>
+    <t>157,3</t>
+  </si>
+  <si>
+    <t>153,5</t>
+  </si>
+  <si>
+    <t>137,4</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>709,8</t>
+  </si>
+  <si>
+    <t>155,7</t>
+  </si>
+  <si>
+    <t>201,2</t>
+  </si>
+  <si>
+    <t>107,1</t>
+  </si>
+  <si>
+    <t>154,5</t>
+  </si>
+  <si>
+    <t>136,7</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>156,2</t>
+  </si>
+  <si>
+    <t>202,8</t>
+  </si>
+  <si>
+    <t>105,4</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>203,7</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>709,2</t>
+  </si>
+  <si>
+    <t>166,5</t>
+  </si>
+  <si>
+    <t>202,4</t>
+  </si>
+  <si>
+    <t>106,3</t>
+  </si>
+  <si>
+    <t>154,6</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>203,6</t>
+  </si>
+  <si>
+    <t>105,7</t>
+  </si>
+  <si>
+    <t>154,1</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>709,0</t>
+  </si>
+  <si>
+    <t>155,5</t>
+  </si>
+  <si>
+    <t>202,0</t>
+  </si>
+  <si>
+    <t>104,5</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>707,6</t>
   </si>
   <si>
     <t>156,1</t>
   </si>
   <si>
-    <t>150,2</t>
-  </si>
-  <si>
-    <t>193,5</t>
-  </si>
-  <si>
-    <t>97,54</t>
-  </si>
-  <si>
-    <t>140,0</t>
-  </si>
-  <si>
-    <t>134,7</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>-753,6</t>
-  </si>
-  <si>
-    <t>156,3</t>
-  </si>
-  <si>
-    <t>150,3</t>
-  </si>
-  <si>
-    <t>193,7</t>
-  </si>
-  <si>
-    <t>97,38</t>
-  </si>
-  <si>
-    <t>140,6</t>
-  </si>
-  <si>
-    <t>133,9</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>-752,8</t>
-  </si>
-  <si>
-    <t>155,5</t>
-  </si>
-  <si>
-    <t>149,7</t>
-  </si>
-  <si>
-    <t>192,9</t>
-  </si>
-  <si>
-    <t>96,89</t>
-  </si>
-  <si>
-    <t>140,3</t>
-  </si>
-  <si>
-    <t>134,1</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>149,6</t>
-  </si>
-  <si>
-    <t>193,4</t>
-  </si>
-  <si>
-    <t>96,62</t>
-  </si>
-  <si>
-    <t>139,6</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>-751,4</t>
-  </si>
-  <si>
-    <t>156,0</t>
-  </si>
-  <si>
-    <t>193,1</t>
-  </si>
-  <si>
-    <t>98,04</t>
-  </si>
-  <si>
-    <t>140,5</t>
-  </si>
-  <si>
-    <t>134,0</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>-752,0</t>
-  </si>
-  <si>
-    <t>155,9</t>
-  </si>
-  <si>
-    <t>149,9</t>
-  </si>
-  <si>
-    <t>192,6</t>
-  </si>
-  <si>
-    <t>98,41</t>
-  </si>
-  <si>
-    <t>139,4</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>-751,7</t>
-  </si>
-  <si>
-    <t>156,2</t>
-  </si>
-  <si>
-    <t>149,8</t>
-  </si>
-  <si>
-    <t>97,17</t>
-  </si>
-  <si>
-    <t>140,4</t>
-  </si>
-  <si>
-    <t>133,8</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>155,8</t>
-  </si>
-  <si>
-    <t>98,02</t>
-  </si>
-  <si>
-    <t>134,8</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>140,2</t>
-  </si>
-  <si>
-    <t>134,2</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>-753,0</t>
-  </si>
-  <si>
-    <t>156,5</t>
-  </si>
-  <si>
-    <t>150,5</t>
-  </si>
-  <si>
-    <t>98,08</t>
-  </si>
-  <si>
-    <t>134,3</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>150,1</t>
-  </si>
-  <si>
-    <t>97,24</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>-754,1</t>
-  </si>
-  <si>
-    <t>193,6</t>
-  </si>
-  <si>
-    <t>97,29</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>-753,8</t>
-  </si>
-  <si>
-    <t>192,7</t>
-  </si>
-  <si>
-    <t>98,09</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>150,0</t>
-  </si>
-  <si>
-    <t>97,93</t>
-  </si>
-  <si>
-    <t>139,8</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>156,4</t>
-  </si>
-  <si>
-    <t>97,91</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>-753,3</t>
-  </si>
-  <si>
-    <t>193,3</t>
-  </si>
-  <si>
-    <t>96,98</t>
-  </si>
-  <si>
-    <t>134,4</t>
-  </si>
-  <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>97,84</t>
+    <t>165,9</t>
+  </si>
+  <si>
+    <t>156,9</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>156,6</t>
+    <t>157,1</t>
+  </si>
+  <si>
+    <t>202,5</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>97,62</t>
-  </si>
-  <si>
-    <t>140,1</t>
-  </si>
-  <si>
-    <t>133,6</t>
+    <t>166,6</t>
+  </si>
+  <si>
+    <t>202,6</t>
+  </si>
+  <si>
+    <t>105,9</t>
   </si>
   <si>
     <t>3,8</t>
-  </si>
-  <si>
-    <t>-754,4</t>
-  </si>
-  <si>
-    <t>193,0</t>
-  </si>
-  <si>
-    <t>97,89</t>
-  </si>
-  <si>
-    <t>141,0</t>
   </si>
 </sst>
 </file>
@@ -760,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -768,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59653935185185192</v>
+        <v>0.77453703703703702</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -909,7 +924,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2686</v>
+        <v>1019</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -938,68 +953,68 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2688</v>
+        <v>1021</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
       </c>
       <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
         <v>44</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>45</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>46</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>47</v>
-      </c>
-      <c r="I24" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25">
+        <v>1020</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="C25">
-        <v>2685</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>54</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>55</v>
-      </c>
-      <c r="I25" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26">
+        <v>1020</v>
+      </c>
+      <c r="D26" t="s">
         <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26">
-        <v>2686</v>
-      </c>
-      <c r="D26" t="s">
-        <v>35</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -1011,10 +1026,10 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" t="s">
         <v>61</v>
-      </c>
-      <c r="I26" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1025,36 +1040,36 @@
         <v>63</v>
       </c>
       <c r="C27">
-        <v>2686</v>
+        <v>1020</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C28">
-        <v>2687</v>
+        <v>1019</v>
       </c>
       <c r="D28" t="s">
         <v>71</v>
@@ -1066,13 +1081,13 @@
         <v>73</v>
       </c>
       <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" t="s">
         <v>74</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>75</v>
-      </c>
-      <c r="I28" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1083,7 +1098,7 @@
         <v>77</v>
       </c>
       <c r="C29">
-        <v>2685</v>
+        <v>1019</v>
       </c>
       <c r="D29" t="s">
         <v>78</v>
@@ -1092,393 +1107,393 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C30">
-        <v>2690</v>
+        <v>1019</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="C31">
-        <v>2684</v>
+        <v>1020</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C32">
-        <v>2686</v>
+        <v>1020</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C33">
-        <v>2686</v>
+        <v>1021</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C34">
-        <v>2684</v>
+        <v>1020</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="H34" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C35">
-        <v>2687</v>
+        <v>1020</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H35" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <v>2686</v>
+        <v>1019</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H36" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="C37">
-        <v>2684</v>
+        <v>1019</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G37" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H37" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C38">
-        <v>2686</v>
+        <v>1018</v>
       </c>
       <c r="D38" t="s">
         <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H38" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s">
-        <v>118</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C39">
-        <v>2687</v>
+        <v>1020</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G39" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="C40">
-        <v>2686</v>
+        <v>1018</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I40" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C41">
-        <v>2685</v>
+        <v>1019</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F41" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42">
+        <v>1017</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
         <v>128</v>
       </c>
-      <c r="C42">
-        <v>2686</v>
-      </c>
-      <c r="D42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
-      </c>
       <c r="F42" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="I42" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
